--- a/data/trans_orig/P74B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P74B-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2007</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23664</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24036</t>
+          <t>23566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45578</t>
+          <t>45010</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152584</t>
+          <t>153509</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168901</t>
+          <t>168836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154665</t>
+          <t>155233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176207</t>
+          <t>176677</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17881</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>15985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34673</t>
+          <t>36190</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135641</t>
+          <t>135410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148938</t>
+          <t>148959</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>139071</t>
+          <t>137554</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157605</t>
+          <t>157759</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>19710</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17731</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25976</t>
+          <t>25935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>24600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45740</t>
+          <t>46643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269305</t>
+          <t>268732</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282297</t>
+          <t>282556</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>270794</t>
+          <t>269891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>292559</t>
+          <t>291934</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45053</t>
+          <t>45600</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73116</t>
+          <t>73413</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74900</t>
+          <t>74473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92960</t>
+          <t>92632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123440</t>
+          <t>121441</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163603</t>
+          <t>163854</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>563957</t>
+          <t>563660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>592020</t>
+          <t>591473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36429</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>584799</t>
+          <t>584548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>624962</t>
+          <t>626961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,77%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20532</t>
+          <t>20472</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72036</t>
+          <t>72009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89673</t>
+          <t>89944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79084</t>
+          <t>79971</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109019</t>
+          <t>109581</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,41%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135828</t>
+          <t>135888</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149401</t>
+          <t>149382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>18315</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>36250</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155600</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>185535</t>
+          <t>184648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>270996</t>
+          <t>271427</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>293980</t>
+          <t>294747</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>273656</t>
+          <t>272630</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>296731</t>
+          <t>295568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48511</t>
+          <t>48080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>25754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47666</t>
+          <t>48692</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86909</t>
+          <t>87961</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>126286</t>
+          <t>129242</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>488369</t>
+          <t>487602</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>524803</t>
+          <t>524709</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>573382</t>
+          <t>569996</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>650946</t>
+          <t>657843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1286503</t>
+          <t>1283547</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1325880</t>
+          <t>1324828</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>87273</t>
+          <t>87367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>123707</t>
+          <t>124474</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1373919</t>
+          <t>1367022</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1451483</t>
+          <t>1454869</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,85%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2012</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2012 (tasa de respuesta: 97,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23875</t>
+          <t>25474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>14360</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28903</t>
+          <t>29219</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24649</t>
+          <t>24761</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49045</t>
+          <t>48927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132798</t>
+          <t>131199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149291</t>
+          <t>149290</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27935</t>
+          <t>28024</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150012</t>
+          <t>150130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174408</t>
+          <t>174296</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30640</t>
+          <t>30267</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32712</t>
+          <t>32629</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33307</t>
+          <t>33019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59422</t>
+          <t>59269</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>137004</t>
+          <t>137377</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156003</t>
+          <t>156173</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12904</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27071</t>
+          <t>27508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153838</t>
+          <t>153991</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179953</t>
+          <t>180241</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29195</t>
+          <t>29369</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>57358</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34090</t>
+          <t>33617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49609</t>
+          <t>49782</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66811</t>
+          <t>66066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101592</t>
+          <t>101896</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>262033</t>
+          <t>260829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>288992</t>
+          <t>288818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>15386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31078</t>
+          <t>31551</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>281762</t>
+          <t>281458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316543</t>
+          <t>317288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,77%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47397</t>
+          <t>47678</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77623</t>
+          <t>76980</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66432</t>
+          <t>65589</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92384</t>
+          <t>91568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119113</t>
+          <t>119064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163331</t>
+          <t>164292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>450849</t>
+          <t>451492</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>481075</t>
+          <t>480794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67734</t>
+          <t>68550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>93686</t>
+          <t>94529</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>525259</t>
+          <t>524298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569477</t>
+          <t>569526</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25287</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48003</t>
+          <t>46326</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>143799</t>
+          <t>143947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>176329</t>
+          <t>176794</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>172929</t>
+          <t>174370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>219871</t>
+          <t>216884</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155120</t>
+          <t>156797</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177836</t>
+          <t>177720</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87389</t>
+          <t>86924</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119919</t>
+          <t>119771</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246970</t>
+          <t>249957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>293912</t>
+          <t>292471</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,65%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>278075</t>
+          <t>279606</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>303287</t>
+          <t>302933</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>279165</t>
+          <t>278691</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>304578</t>
+          <t>302755</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34219</t>
+          <t>34573</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59431</t>
+          <t>57900</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59591</t>
+          <t>60065</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148641</t>
+          <t>148660</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>200744</t>
+          <t>199512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>592607</t>
+          <t>591036</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>652211</t>
+          <t>650157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>749234</t>
+          <t>749580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>842971</t>
+          <t>842464</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,79%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1174605</t>
+          <t>1175837</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1226708</t>
+          <t>1226689</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>262299</t>
+          <t>264353</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321903</t>
+          <t>323474</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1446888</t>
+          <t>1447395</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1540625</t>
+          <t>1540279</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2016</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2016 (tasa de respuesta: 94,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28406</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>29879</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32547</t>
+          <t>31679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56095</t>
+          <t>55894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101768</t>
+          <t>102047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118137</t>
+          <t>118109</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26496</t>
+          <t>26509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117098</t>
+          <t>117299</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140646</t>
+          <t>141514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,71%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15015</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33359</t>
+          <t>32579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>11426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>24296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>29805</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52315</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123812</t>
+          <t>124592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142156</t>
+          <t>142546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17313</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>30521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146803</t>
+          <t>146976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>170122</t>
+          <t>169313</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,03%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23823</t>
+          <t>23536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45539</t>
+          <t>45685</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24378</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51280</t>
+          <t>51715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82381</t>
+          <t>82084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>222128</t>
+          <t>221982</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243844</t>
+          <t>244131</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22254</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>231918</t>
+          <t>232215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>263019</t>
+          <t>262584</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,55%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44551</t>
+          <t>45097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72988</t>
+          <t>74140</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73860</t>
+          <t>74950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99662</t>
+          <t>100655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123275</t>
+          <t>124379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>167430</t>
+          <t>168011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>462078</t>
+          <t>460926</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>490515</t>
+          <t>489969</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62412</t>
+          <t>61419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88214</t>
+          <t>87124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>529709</t>
+          <t>529128</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>573864</t>
+          <t>572760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>25578</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49390</t>
+          <t>47865</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108151</t>
+          <t>109122</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138850</t>
+          <t>139478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138074</t>
+          <t>139566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181243</t>
+          <t>183855</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>211051</t>
+          <t>212576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>234672</t>
+          <t>234863</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100542</t>
+          <t>99914</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131241</t>
+          <t>130270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>318590</t>
+          <t>315978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>361759</t>
+          <t>360267</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>290793</t>
+          <t>291284</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>317894</t>
+          <t>317244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>289545</t>
+          <t>290333</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>318640</t>
+          <t>318492</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40036</t>
+          <t>40686</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67137</t>
+          <t>66646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>45627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>73786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146527</t>
+          <t>146637</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195771</t>
+          <t>194536</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>556055</t>
+          <t>556855</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>614557</t>
+          <t>613437</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>711984</t>
+          <t>712868</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>807434</t>
+          <t>805915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1160936</t>
+          <t>1162171</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1210180</t>
+          <t>1210070</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>276437</t>
+          <t>277557</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>334939</t>
+          <t>334139</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1440267</t>
+          <t>1441786</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1535717</t>
+          <t>1534833</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P74B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P74B-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22069</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>16355</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23662</t>
+          <t>23679</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23566</t>
+          <t>23888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45010</t>
+          <t>46831</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153509</t>
+          <t>152921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168836</t>
+          <t>168461</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155233</t>
+          <t>153412</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176677</t>
+          <t>176355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36190</t>
+          <t>34633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135410</t>
+          <t>136093</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148959</t>
+          <t>149315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137554</t>
+          <t>139111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>157759</t>
+          <t>158075</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>19070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17377</t>
+          <t>17113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>25622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>24087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46643</t>
+          <t>45358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268732</t>
+          <t>269372</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282556</t>
+          <t>282301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269891</t>
+          <t>271176</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>291934</t>
+          <t>292447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45600</t>
+          <t>45346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73413</t>
+          <t>73669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74473</t>
+          <t>74435</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92632</t>
+          <t>92816</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121441</t>
+          <t>123172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163854</t>
+          <t>165501</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>563660</t>
+          <t>563404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>591473</t>
+          <t>591727</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18697</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>36894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>584548</t>
+          <t>582901</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>626961</t>
+          <t>625230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20472</t>
+          <t>21568</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72009</t>
+          <t>71318</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89944</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79971</t>
+          <t>79695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109581</t>
+          <t>109637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135888</t>
+          <t>134792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149382</t>
+          <t>149296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>19048</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36250</t>
+          <t>36941</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155038</t>
+          <t>154982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>184648</t>
+          <t>184924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>271427</t>
+          <t>271910</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>294747</t>
+          <t>294109</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>272630</t>
+          <t>273120</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>295568</t>
+          <t>296817</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,37%</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24760</t>
+          <t>25398</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48080</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>24505</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>48692</t>
+          <t>48202</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87961</t>
+          <t>86750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129242</t>
+          <t>125132</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>487602</t>
+          <t>486902</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>524709</t>
+          <t>525540</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>569996</t>
+          <t>572778</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>657843</t>
+          <t>658955</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1283547</t>
+          <t>1287657</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1324828</t>
+          <t>1326039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>87367</t>
+          <t>86536</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>124474</t>
+          <t>125174</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1367022</t>
+          <t>1365910</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1454869</t>
+          <t>1452087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25474</t>
+          <t>23558</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29219</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24761</t>
+          <t>24696</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>50627</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131199</t>
+          <t>133115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149290</t>
+          <t>149657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28024</t>
+          <t>27602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150130</t>
+          <t>148430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174296</t>
+          <t>174361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30267</t>
+          <t>31429</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32629</t>
+          <t>32427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33019</t>
+          <t>32896</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59269</t>
+          <t>60960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>137377</t>
+          <t>136215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156173</t>
+          <t>155440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27508</t>
+          <t>27243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>153991</t>
+          <t>152300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180241</t>
+          <t>180364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29369</t>
+          <t>29865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57358</t>
+          <t>57757</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33617</t>
+          <t>33713</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49782</t>
+          <t>49474</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66066</t>
+          <t>67252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101896</t>
+          <t>102132</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>260829</t>
+          <t>260430</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>288818</t>
+          <t>288322</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31551</t>
+          <t>31455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>281458</t>
+          <t>281222</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>317288</t>
+          <t>316102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47678</t>
+          <t>48034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76980</t>
+          <t>79846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65589</t>
+          <t>64873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91568</t>
+          <t>91967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119064</t>
+          <t>121433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164292</t>
+          <t>164447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>451492</t>
+          <t>448626</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>480794</t>
+          <t>480438</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68550</t>
+          <t>68151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94529</t>
+          <t>95245</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>524298</t>
+          <t>524143</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569526</t>
+          <t>567157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46326</t>
+          <t>47056</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>143947</t>
+          <t>144571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>176794</t>
+          <t>176354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>174370</t>
+          <t>176407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>216884</t>
+          <t>220967</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>156797</t>
+          <t>156067</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177720</t>
+          <t>178251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86924</t>
+          <t>87364</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119771</t>
+          <t>119147</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>249957</t>
+          <t>245874</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292471</t>
+          <t>290434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>279606</t>
+          <t>277465</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>302933</t>
+          <t>303289</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>278691</t>
+          <t>278071</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>302755</t>
+          <t>303526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34573</t>
+          <t>34217</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57900</t>
+          <t>60041</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36001</t>
+          <t>35230</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60065</t>
+          <t>60685</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148660</t>
+          <t>147863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>199512</t>
+          <t>200353</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>591036</t>
+          <t>589258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>650157</t>
+          <t>650270</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>749580</t>
+          <t>745411</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>842464</t>
+          <t>842028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1175837</t>
+          <t>1174996</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1226689</t>
+          <t>1227486</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>264353</t>
+          <t>264240</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>323474</t>
+          <t>325252</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1447395</t>
+          <t>1447831</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1540279</t>
+          <t>1544448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,45%</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28127</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>32086</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55894</t>
+          <t>54995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102047</t>
+          <t>101386</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>118109</t>
+          <t>117633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26509</t>
+          <t>26120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117299</t>
+          <t>118198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>141514</t>
+          <t>141107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,47%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>32978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>25109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29805</t>
+          <t>29407</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52142</t>
+          <t>52551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>124592</t>
+          <t>124193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142546</t>
+          <t>142750</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>16838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30521</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146976</t>
+          <t>146567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169313</t>
+          <t>169711</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23536</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45685</t>
+          <t>45904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>24628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>37920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51715</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82084</t>
+          <t>82180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>221982</t>
+          <t>221763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244131</t>
+          <t>243997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>22004</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>232215</t>
+          <t>232119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262584</t>
+          <t>262925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45097</t>
+          <t>42436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74950</t>
+          <t>74361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100655</t>
+          <t>101166</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124379</t>
+          <t>125569</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168011</t>
+          <t>166318</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>460926</t>
+          <t>463040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>489969</t>
+          <t>492630</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61419</t>
+          <t>60908</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87124</t>
+          <t>87713</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>529128</t>
+          <t>530821</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>572760</t>
+          <t>571570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25578</t>
+          <t>25826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>47826</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109122</t>
+          <t>106363</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139478</t>
+          <t>137532</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139566</t>
+          <t>140009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183855</t>
+          <t>181267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>212576</t>
+          <t>212615</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>234863</t>
+          <t>234615</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99914</t>
+          <t>101860</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130270</t>
+          <t>133029</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>315978</t>
+          <t>318566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>360267</t>
+          <t>359824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,99%</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>291284</t>
+          <t>290102</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>317244</t>
+          <t>319066</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>290333</t>
+          <t>287922</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>318492</t>
+          <t>318734</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40686</t>
+          <t>38864</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66646</t>
+          <t>67828</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45627</t>
+          <t>45385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73786</t>
+          <t>76197</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>146637</t>
+          <t>146115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>194536</t>
+          <t>194579</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>556855</t>
+          <t>555097</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>613437</t>
+          <t>617764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>712868</t>
+          <t>716450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>805915</t>
+          <t>810070</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1162171</t>
+          <t>1162128</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1210070</t>
+          <t>1210592</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>277557</t>
+          <t>273230</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>334139</t>
+          <t>335897</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1441786</t>
+          <t>1437631</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1534833</t>
+          <t>1531251</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
